--- a/Bitacora_Sprint1_Grupo5.xlsx
+++ b/Bitacora_Sprint1_Grupo5.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{995D11B4-010F-49D4-BEF7-9152CF2DCFC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="23880" yWindow="-2820" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId5"/>
+    <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -43,9 +52,6 @@
     <t>Estado</t>
   </si>
   <si>
-    <t>Rocío Spaventa</t>
-  </si>
-  <si>
     <t>Security Lead</t>
   </si>
   <si>
@@ -155,28 +161,33 @@
   </si>
   <si>
     <t>Evidencia de producción propia exigida por la cátedra</t>
+  </si>
+  <si>
+    <t>Brandan Joaquin</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="3">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
@@ -186,11 +197,17 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FFC4C7C5"/>
@@ -204,68 +221,64 @@
       <bottom style="thin">
         <color rgb="FFC4C7C5"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF356854"/>
-          <bgColor rgb="FF356854"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-      <border/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="&quot;Google Sans Text&quot;"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <border>
@@ -283,46 +296,70 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="Hoja 1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="Hoja 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="4"/>
+      <tableStyleElement type="firstRowStripe" dxfId="3"/>
+      <tableStyleElement type="secondRowStripe" dxfId="2"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J8" displayName="Tabla_1" name="Tabla_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla_1" displayName="Tabla_1" ref="A1:J8">
   <tableColumns count="10">
-    <tableColumn name="Fecha" id="1"/>
-    <tableColumn name="Integrante" id="2"/>
-    <tableColumn name="Rol" id="3"/>
-    <tableColumn name="Actividad realizada" id="4"/>
-    <tableColumn name="Resultado / evidencia" id="5"/>
-    <tableColumn name="Problema encontrado" id="6"/>
-    <tableColumn name="Solución aplicada" id="7"/>
-    <tableColumn name="Decisión y fundamento" id="8"/>
-    <tableColumn name="Planeado vs. ejecutado" id="9"/>
-    <tableColumn name="Estado" id="10"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Integrante" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Rol"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Actividad realizada"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Resultado / evidencia"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Problema encontrado"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Solución aplicada"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Decisión y fundamento"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Planeado vs. ejecutado"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Estado"/>
   </tableColumns>
-  <tableStyleInfo name="Hoja 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Hoja 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -512,28 +549,31 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="13.38"/>
-    <col customWidth="1" min="2" max="2" width="13.88"/>
-    <col customWidth="1" min="3" max="3" width="22.88"/>
-    <col customWidth="1" min="4" max="4" width="37.63"/>
-    <col customWidth="1" min="5" max="5" width="37.5"/>
-    <col customWidth="1" min="6" max="6" width="37.63"/>
-    <col customWidth="1" min="7" max="7" width="33.5"/>
-    <col customWidth="1" min="8" max="8" width="37.63"/>
-    <col customWidth="1" min="9" max="9" width="32.63"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="37.5703125" customWidth="1"/>
+    <col min="5" max="5" width="37.42578125" customWidth="1"/>
+    <col min="6" max="6" width="37.5703125" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" customWidth="1"/>
+    <col min="8" max="8" width="37.5703125" customWidth="1"/>
+    <col min="9" max="9" width="32.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row r="1" spans="1:10" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -565,239 +605,239 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
+    <row r="2" spans="1:10" ht="22.5" customHeight="1">
       <c r="A2" s="2">
-        <v>46282.0</v>
+        <v>46282</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:10" ht="22.5" customHeight="1">
+      <c r="A3" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="C3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="2">
-        <v>46282.0</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="4" spans="1:10" ht="22.5" customHeight="1">
+      <c r="A4" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="22.5" customHeight="1">
+      <c r="A5" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="22.5" customHeight="1">
+      <c r="A6" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="4" t="s">
+      <c r="D6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="22.5" customHeight="1">
+      <c r="A7" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="22.5" customHeight="1">
+      <c r="A8" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="2">
-        <v>46282.0</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="C8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="2">
-        <v>46283.0</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="2">
-        <v>46283.0</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="2">
-        <v>46283.0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="2">
-        <v>46286.0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A8">
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A8" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>